--- a/data/gravel/Trek Checkmate 2025.xlsx
+++ b/data/gravel/Trek Checkmate 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08E4931-CBCF-1C42-9C4F-CFDCA839C9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF3DAAA-1C15-FE4B-A780-C97F8EE11B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29740" yWindow="-17500" windowWidth="25020" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -803,19 +803,19 @@
         <v>700</v>
       </c>
       <c r="D9">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E9">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F9">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="G9">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="H9">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="J9">
         <v>700</v>
@@ -1044,27 +1044,27 @@
         <v>96</v>
       </c>
       <c r="C14">
-        <f>J14*10</f>
+        <f t="shared" ref="C14:C26" si="4">J14*10</f>
         <v>532</v>
       </c>
       <c r="D14">
-        <f t="shared" ref="D14:H26" si="4">K14*10</f>
+        <f t="shared" ref="D14:H26" si="5">K14*10</f>
         <v>540</v>
       </c>
       <c r="E14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>555</v>
       </c>
       <c r="F14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>570</v>
       </c>
       <c r="G14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>581</v>
       </c>
       <c r="H14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>592</v>
       </c>
       <c r="J14">
@@ -1094,27 +1094,27 @@
         <v>97</v>
       </c>
       <c r="C15">
-        <f>J15*10</f>
-        <v>80</v>
-      </c>
-      <c r="D15">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
+      <c r="D15">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
       <c r="E15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="F15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="G15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="H15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="J15">
@@ -1144,27 +1144,27 @@
         <v>98</v>
       </c>
       <c r="C16">
-        <f>J16*10</f>
-        <v>426</v>
-      </c>
-      <c r="D16">
         <f t="shared" si="4"/>
         <v>426</v>
       </c>
+      <c r="D16">
+        <f t="shared" si="5"/>
+        <v>426</v>
+      </c>
       <c r="E16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>426</v>
       </c>
       <c r="F16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>426</v>
       </c>
       <c r="G16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>426</v>
       </c>
       <c r="H16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>426</v>
       </c>
       <c r="J16">
@@ -1194,27 +1194,27 @@
         <v>99</v>
       </c>
       <c r="C17">
-        <f>J17*10</f>
-        <v>49</v>
-      </c>
-      <c r="D17">
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
+      <c r="D17">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
       <c r="E17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="F17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="G17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="H17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="J17">
@@ -1244,27 +1244,27 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <f>J18*10</f>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="D18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="E18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>68</v>
       </c>
       <c r="F18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="G18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>65</v>
       </c>
       <c r="H18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>62</v>
       </c>
       <c r="J18">
@@ -1294,27 +1294,27 @@
         <v>101</v>
       </c>
       <c r="C19">
-        <f>J19*10</f>
+        <f t="shared" si="4"/>
         <v>1003</v>
       </c>
       <c r="D19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1011</v>
       </c>
       <c r="E19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1022</v>
       </c>
       <c r="F19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1035</v>
       </c>
       <c r="G19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1045</v>
       </c>
       <c r="H19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1054</v>
       </c>
       <c r="J19">
@@ -1344,27 +1344,27 @@
         <v>102</v>
       </c>
       <c r="C20">
-        <f>J20*10</f>
+        <f t="shared" si="4"/>
         <v>718</v>
       </c>
       <c r="D20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>747</v>
       </c>
       <c r="E20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>782</v>
       </c>
       <c r="F20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>816</v>
       </c>
       <c r="G20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>851</v>
       </c>
       <c r="H20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>886</v>
       </c>
       <c r="J20">
@@ -1394,27 +1394,27 @@
         <v>103</v>
       </c>
       <c r="C21">
-        <f>J21*10</f>
+        <f t="shared" si="4"/>
         <v>380</v>
       </c>
       <c r="D21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>385</v>
       </c>
       <c r="E21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>392</v>
       </c>
       <c r="F21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>399</v>
       </c>
       <c r="G21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>404</v>
       </c>
       <c r="H21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>409</v>
       </c>
       <c r="J21">
@@ -1444,27 +1444,27 @@
         <v>104</v>
       </c>
       <c r="C22">
-        <f>J22*10</f>
+        <f t="shared" si="4"/>
         <v>525</v>
       </c>
       <c r="D22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>540</v>
       </c>
       <c r="E22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>560</v>
       </c>
       <c r="F22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>584</v>
       </c>
       <c r="G22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>608</v>
       </c>
       <c r="H22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>633</v>
       </c>
       <c r="J22">
@@ -1494,27 +1494,27 @@
         <v>88</v>
       </c>
       <c r="C23">
-        <f>J23*10</f>
+        <f t="shared" si="4"/>
         <v>546</v>
       </c>
       <c r="D23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>587</v>
       </c>
       <c r="E23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>628</v>
       </c>
       <c r="F23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>668</v>
       </c>
       <c r="G23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>720</v>
       </c>
       <c r="H23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>751</v>
       </c>
       <c r="J23">
@@ -1544,27 +1544,27 @@
         <v>89</v>
       </c>
       <c r="C24">
-        <f>J24*10</f>
+        <f t="shared" si="4"/>
         <v>611</v>
       </c>
       <c r="D24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>652</v>
       </c>
       <c r="E24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>693</v>
       </c>
       <c r="F24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>733</v>
       </c>
       <c r="G24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>785</v>
       </c>
       <c r="H24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>816</v>
       </c>
       <c r="J24">
@@ -1594,27 +1594,27 @@
         <v>90</v>
       </c>
       <c r="C25">
-        <f>J25*10</f>
+        <f t="shared" si="4"/>
         <v>586</v>
       </c>
       <c r="D25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>627</v>
       </c>
       <c r="E25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>668</v>
       </c>
       <c r="F25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>708</v>
       </c>
       <c r="G25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>760</v>
       </c>
       <c r="H25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>791</v>
       </c>
       <c r="J25">
@@ -1644,27 +1644,27 @@
         <v>91</v>
       </c>
       <c r="C26">
-        <f>J26*10</f>
+        <f t="shared" si="4"/>
         <v>651</v>
       </c>
       <c r="D26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>692</v>
       </c>
       <c r="E26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>733</v>
       </c>
       <c r="F26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>773</v>
       </c>
       <c r="G26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>825</v>
       </c>
       <c r="H26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>856</v>
       </c>
       <c r="J26">

--- a/data/gravel/Trek Checkmate 2025.xlsx
+++ b/data/gravel/Trek Checkmate 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF3DAAA-1C15-FE4B-A780-C97F8EE11B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE94C71-9F9F-0343-AB1B-631AE26841B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29740" yWindow="-17500" windowWidth="25020" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>a8:h35</t>
+  </si>
+  <si>
+    <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_auto,f_auto,fl_progressive:semi,q_auto/TK25_WEB_FDP_RoadGravel_MY25-Checkmate-SLR_Lifestyle__Afternoon_A7R4-01923_4000x3000</t>
   </si>
 </sst>
 </file>
@@ -758,6 +761,11 @@
         <v>86</v>
       </c>
     </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+    </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Trek Checkmate 2025.xlsx
+++ b/data/gravel/Trek Checkmate 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE94C71-9F9F-0343-AB1B-631AE26841B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DD7EC9-9BE0-6D47-A09F-BB40A93F5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29740" yWindow="-17500" windowWidth="25020" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_auto,f_auto,fl_progressive:semi,q_auto/TK25_WEB_FDP_RoadGravel_MY25-Checkmate-SLR_Lifestyle__Afternoon_A7R4-01923_4000x3000</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Waterloo, Wisconsin, USA</t>
   </si>
 </sst>
 </file>
@@ -714,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -2103,6 +2109,14 @@
         <v>105</v>
       </c>
     </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Trek Checkmate 2025.xlsx
+++ b/data/gravel/Trek Checkmate 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DD7EC9-9BE0-6D47-A09F-BB40A93F5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE24C888-BB9F-A047-B9A8-45ABEF28F4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>Waterloo, Wisconsin, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -720,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
@@ -1955,165 +1973,195 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58">
-        <v>180</v>
+        <v>54</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59">
-        <v>180</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>64</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>65</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>72</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B72">
-        <v>4399</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B73">
-        <v>8199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78">
+        <v>4399</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B79">
+        <v>8199</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>78</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>114</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>115</v>
       </c>
     </row>
